--- a/inventory/files/2026-W42/Q4_ship_plan_2026-W42.xlsx
+++ b/inventory/files/2026-W42/Q4_ship_plan_2026-W42.xlsx
@@ -446,7 +446,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Q4 shipment files, 2026-W42 (as of 2026-10-19)</t>
+          <t>Q4 shipment files, 2026-W42 (as of 2026-10-22)</t>
         </is>
       </c>
     </row>
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>111557</v>
+        <v>94842</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3895</v>
+        <v>2485</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -541,7 +541,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>16270</v>
+        <v>14573</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -562,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9224</v>
+        <v>9508</v>
       </c>
       <c r="E8" t="n">
         <v>9</v>
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>785</v>
+        <v>823</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
@@ -604,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>3070</v>
+        <v>2512</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>877</v>
+        <v>1003</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>1390</v>
+        <v>1608</v>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -773,13 +773,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79170</v>
+        <v>67305</v>
       </c>
       <c r="C2" t="n">
         <v>105</v>
       </c>
       <c r="D2" t="n">
-        <v>754</v>
+        <v>641</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>79074</v>
+        <v>67231</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -800,17 +800,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.6</v>
+        <v>23.2</v>
       </c>
       <c r="J2" t="n">
-        <v>25225</v>
+        <v>37320</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8459</v>
+        <v>8693</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8459</v>
+        <v>8693</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -858,17 +858,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4641</v>
+        <v>4475</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6597</v>
+        <v>6720</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6597</v>
+        <v>6720</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -916,17 +916,17 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>1093</v>
+        <v>846</v>
       </c>
       <c r="K4" t="n">
-        <v>3361</v>
+        <v>3360</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -936,10 +936,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>top FBA SKU by 30-day FBA units</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>AH-RCPAINT</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>US</t>
@@ -953,7 +957,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5824</v>
+        <v>5052</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -966,7 +970,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5824</v>
+        <v>5052</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -974,17 +978,17 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>1269</v>
+        <v>1146</v>
       </c>
       <c r="K5" t="n">
-        <v>1920</v>
+        <v>2880</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1011,13 +1015,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3300</v>
+        <v>2100</v>
       </c>
       <c r="C6" t="n">
         <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1030,7 +1034,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3170</v>
+        <v>1982</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1038,17 +1042,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2110</v>
+        <v>2236</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1075,7 +1079,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1739</v>
+        <v>1386</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1088,7 +1092,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1739</v>
+        <v>1386</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1096,17 +1100,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>13.6</v>
+        <v>23.7</v>
       </c>
       <c r="J7" t="n">
-        <v>270</v>
+        <v>413</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1129,30 +1133,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AH-828A</t>
+          <t>AH-PROPAINTKITA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1350</v>
+        <v>776</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B08FF6X75N</t>
+          <t>B0CN8HJSYM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ceramic Headlight Restoration Detailer Pack</t>
+          <t>Ceramic Coating for Cars</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1328</v>
+        <v>770</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1160,17 +1164,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>15.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>370</v>
+        <v>110</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1193,24 +1197,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-828A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1050</v>
+        <v>510</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B0FW6WFX4D</t>
+          <t>B08FF6X75N</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Wheel Sealant Spray</t>
+          <t>Ceramic Headlight Restoration Detailer Pack</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1050</v>
+        <v>487</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1218,22 +1228,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>20.3</v>
+        <v>16.5</v>
       </c>
       <c r="J9" t="n">
-        <v>481</v>
+        <v>400</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MISSING: NIC to add units per box</t>
+          <t>Seller Central case pack 2026-09-28</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1251,42 +1261,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-TRPROAUPC</t>
+          <t>AH-RCPL-QA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>779</v>
+        <v>479</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B0C4QX35KX</t>
+          <t>B0H1NM7467</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceramic Trim Coat Black Plastic Restorer for Cars</t>
+          <t>Rapid Ceramic Plastic Restorer and Protectant Pro Pack</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>779</v>
+        <v>479</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1309,30 +1319,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-PROPAINTKITA</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>768</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>96</v>
+        <v>466</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B0CN8HJSYM</t>
+          <t>B0FW6WFX4D</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceramic Coating for Cars</t>
+          <t>Rapid Ceramic Wheel Sealant Spray</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>767</v>
+        <v>466</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1340,22 +1344,22 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>20.9</v>
       </c>
       <c r="J11" t="n">
-        <v>130</v>
+        <v>503</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>600</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Seller Central case pack 2026-09-28</t>
+          <t>MISSING: NIC to add units per box</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1373,24 +1377,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCTIRE-QA</t>
+          <t>AH-TRPROAUPC</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>511</v>
+        <v>269</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B0GY1XLQMS</t>
+          <t>B0C4QX35KX</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Tire Coat</t>
+          <t>Ceramic Trim Coat Black Plastic Restorer for Cars</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>511</v>
+        <v>269</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1398,17 +1402,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>20.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>657</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1431,42 +1435,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AH-RCPL-QA</t>
+          <t>AH-VEHSHAM16A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>483</v>
+        <v>208</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B0H1NM7467</t>
+          <t>B0DVB4P9KQ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Plastic Restorer and Protectant Pro Pack</t>
+          <t>High Foam Vehicle Shampoo</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>483</v>
+        <v>208</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>41.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="K13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1489,24 +1493,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AH-SPONGE3A</t>
+          <t>AH-RCINT14-2PA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>366</v>
+        <v>204</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B0DH5HKH5R</t>
+          <t>B0DKVBTNNT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Premium Microfiber Applicator Pads for Cars</t>
+          <t>Rapid Ceramic Interior Detailer and Protectant Spray</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>195</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1514,30 +1524,34 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>26.3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>368</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>MISSING: NIC to add units per box</t>
+          <t>Seller Central case pack 2026-09-28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>top FBA SKU by 30-day FBA units</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>AH-RCINT14-2P</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>US</t>
@@ -1547,42 +1561,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AH-RCPAINTQA</t>
+          <t>AH-PROPTKTPP16A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B0C4ZVMRRK</t>
+          <t>B0HKBPRXSV</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Paint Sealant</t>
+          <t>Ceramic Coating for Cars</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>245</v>
+        <v>148</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BELOW_TARGET</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>1006</v>
+        <v>78</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1592,14 +1606,10 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>top FBA SKU by 30-day FBA units</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>AH-RCPAINT-QA, AH-RCPAINT-QAUPC, AHW-104QA</t>
-        </is>
-      </c>
+          <t>only FBA SKU</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>US</t>
@@ -1609,30 +1619,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AH-RCINT14-2PA</t>
+          <t>AH-RCPV14A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>180</v>
-      </c>
-      <c r="C16" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B0DKVBTNNT</t>
+          <t>B0H1NP4461</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Interior Detailer and Protectant Spray</t>
+          <t>Rapid Ceramic PPF and Vinyl Protective Sealant Spray</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1640,34 +1644,30 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.7</v>
+        <v>23.9</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Seller Central case pack 2026-09-28</t>
+          <t>MISSING: NIC to add units per box</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>top FBA SKU by 30-day FBA units</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>AH-RCINT14-2P</t>
-        </is>
-      </c>
+          <t>only FBA SKU</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>US</t>
@@ -1677,24 +1677,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AH-VEHSHAM16A</t>
+          <t>AH-FOAMAPP3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>168</v>
+        <v>120</v>
+      </c>
+      <c r="C17" t="n">
+        <v>120</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B0DVB4P9KQ</t>
+          <t>B0DH5ZC1N4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>High Foam Vehicle Shampoo</t>
+          <t>Foam Applicator Pads for Tire Coating</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1702,22 +1708,22 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>46.6</v>
+        <v>30.3</v>
       </c>
       <c r="J17" t="n">
-        <v>494</v>
+        <v>195</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MISSING: NIC to add units per box</t>
+          <t>Seller Central case pack 2026-09-28</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1739,13 +1745,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="C18" t="n">
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1758,7 +1764,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1766,17 +1772,17 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="J18" t="n">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1799,24 +1805,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AH-RCPV14A</t>
+          <t>AH-811A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>145</v>
+        <v>56</v>
+      </c>
+      <c r="C19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B0H1NP4461</t>
+          <t>B08DDJ49X7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rapid Ceramic PPF and Vinyl Protective Sealant Spray</t>
+          <t>Ceramic Headlight Restoration Detailer Pack</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1824,22 +1836,22 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>21.2</v>
+        <v>55.8</v>
       </c>
       <c r="J19" t="n">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="K19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MISSING: NIC to add units per box</t>
+          <t>Seller Central case pack 2026-09-28</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1857,48 +1869,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AH-FOAMAPP3</t>
+          <t>AH-MFDRYTWLA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="C20" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B0DH5ZC1N4</t>
+          <t>B0FX5WH19H</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foam Applicator Pads for Tire Coating</t>
+          <t>Premium Microfiber Drying Towel for Cars</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1921,48 +1933,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AH-PROMARKITA</t>
+          <t>AH-RCINT-QA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B0H3QRH9B7</t>
+          <t>B0H1NDSGVJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Professional Ceramic Marine Coating</t>
+          <t>Rapid Ceramic Interior Detailer and Protectant Pro Pack</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>BELOW_TARGET</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>28.8</v>
+        <v>64</v>
       </c>
       <c r="J21" t="n">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1985,30 +1997,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AH-811A</t>
+          <t>AH-PROPVKITA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B08DDJ49X7</t>
+          <t>B0H3QLBNZF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceramic Headlight Restoration Detailer Pack</t>
+          <t>Professional Ceramic PPF/Vinyl Coating</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2016,17 +2028,17 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>66.90000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="J22" t="n">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2049,48 +2061,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AH-MFDRYTWLA</t>
+          <t>AH-PROWHLKITA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B0FX5WH19H</t>
+          <t>B0GYBH76BR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Premium Microfiber Drying Towel for Cars</t>
+          <t>Ceramic Coating for Wheels and Rims</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2113,53 +2125,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AH-GCLEAN-B16A</t>
+          <t>AH-RCPV-QA</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>B0H1SP98C3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rapid Ceramic PPF and Vinyl Protective Sealant</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>BELOW_FLOOR</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
         <v>20</v>
       </c>
-      <c r="C24" t="n">
-        <v>20</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>B0GZSHD4GP</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Glass Cleaner for Cars</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>11</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>BELOW_FLOOR</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>56</v>
-      </c>
-      <c r="K24" t="n">
-        <v>60</v>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Seller Central case pack 2026-09-28</t>
+          <t>MISSING: NIC to add units per box</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2177,30 +2183,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AH-RCINT-QA</t>
+          <t>AH-BNDL-COREA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B0H1NDSGVJ</t>
+          <t>B0F2JL4F2W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Interior Detailer and Protectant Pro Pack</t>
+          <t>Ceramic Car Wash Kit</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2208,17 +2214,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>65.8</v>
+        <v>57.8</v>
       </c>
       <c r="J25" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2233,134 +2239,6 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AH-RCACA</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>20</v>
-      </c>
-      <c r="C26" t="n">
-        <v>20</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>B0F2JBJXYJ</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Rapid Ceramic Aircraft Protective Coating (14 oz.)</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>58</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Seller Central case pack 2026-09-28</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AH-PROPVKITA</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>8</v>
-      </c>
-      <c r="C27" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>B0H3QLBNZF</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Professional Ceramic PPF/Vinyl Coating</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>51</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Seller Central case pack 2026-09-28</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
         <is>
           <t>US</t>
         </is>
@@ -2377,7 +2255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2487,7 +2365,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1948</v>
+        <v>2316</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2500,7 +2378,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1948</v>
+        <v>2316</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2508,17 +2386,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>59.9</v>
+        <v>57.9</v>
       </c>
       <c r="J2" t="n">
-        <v>7617</v>
+        <v>7255</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2541,24 +2419,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1164</v>
+        <v>161</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B0FYRJ1966</t>
+          <t>B0FW6WFX4D</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Plastic Restorer and Protectant Spray</t>
+          <t>Rapid Ceramic Wheel Sealant Spray</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1164</v>
+        <v>161</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2566,17 +2444,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.6</v>
+        <v>41.8</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>198</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2599,42 +2477,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AH-RCTIRE10A</t>
+          <t>AH-REPAIRHL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>611</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B0F45C2YHV</t>
+          <t>B0GT6FZRL1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Tire Coat</t>
+          <t>Headlight Repair Kits</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>611</v>
+        <v>5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>45.9</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1062</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2657,42 +2535,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-MFDRYTWLA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B0FW6WFX4D</t>
+          <t>B0FX5WH19H</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Wheel Sealant Spray</t>
+          <t>Premium Microfiber Drying Towel for Cars</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>43.9</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2707,180 +2585,6 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AH-VEHSHAM16A</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>23</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>B0DVB4P9KQ</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>High Foam Vehicle Shampoo</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>23</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>BELOW_TARGET</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>62</v>
-      </c>
-      <c r="J6" t="n">
-        <v>101</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>MISSING: NIC to add units per box</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AH-REPAIRHL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>B0GT6FZRL1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Headlight Repair Kits</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>MISSING: NIC to add units per box</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AH-MFDRYTWLA</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>B0FX5WH19H</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Premium Microfiber Drying Towel for Cars</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>MISSING: NIC to add units per box</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
@@ -3007,7 +2711,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13798</v>
+        <v>12875</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3020,7 +2724,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13798</v>
+        <v>12875</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3028,17 +2732,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3517</v>
+        <v>3175</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>527</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -3065,7 +2769,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1128</v>
+        <v>1024</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -3078,25 +2782,25 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1128</v>
+        <v>1024</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BELOW_TARGET</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>62.6</v>
+        <v>68.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1420</v>
+        <v>1462</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3123,7 +2827,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>726</v>
+        <v>366</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3136,7 +2840,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>726</v>
+        <v>366</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3144,17 +2848,17 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>16.2</v>
+        <v>15.7</v>
       </c>
       <c r="J4" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3181,7 +2885,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3194,7 +2898,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3202,17 +2906,17 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>18.8</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3239,7 +2943,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3252,7 +2956,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3260,17 +2964,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>66.7</v>
+        <v>64.2</v>
       </c>
       <c r="J6" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3280,10 +2984,14 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>top FBA SKU by 30-day FBA units</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>AH-RCPAINT</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>UK</t>
@@ -3297,7 +3005,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3310,7 +3018,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3318,17 +3026,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>31.3</v>
+        <v>22.1</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3469,7 +3177,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4664</v>
+        <v>4786</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3482,7 +3190,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4664</v>
+        <v>4786</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3490,17 +3198,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>39.5</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2938</v>
+        <v>2753</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -3558,7 +3266,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3585,7 +3293,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>651</v>
+        <v>738</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3598,7 +3306,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>651</v>
+        <v>738</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -3606,17 +3314,17 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>21.4</v>
+        <v>17.5</v>
       </c>
       <c r="J4" t="n">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="K4" t="n">
         <v>210</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3643,7 +3351,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -3656,7 +3364,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3674,7 +3382,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3701,7 +3409,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -3714,7 +3422,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3732,7 +3440,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3763,7 +3471,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -3776,7 +3484,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3784,17 +3492,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>38.7</v>
+        <v>34.5</v>
       </c>
       <c r="J7" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3852,7 +3560,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3910,7 +3618,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3937,7 +3645,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -3950,7 +3658,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3958,17 +3666,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>106.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4109,7 +3817,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4122,7 +3830,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4140,7 +3848,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -4198,7 +3906,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -4256,7 +3964,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -4279,42 +3987,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AH-RCINT14A1</t>
+          <t>AH-RCPAINTA1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B0DKVZRX69</t>
+          <t>B0B94G13CN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Interior Detailer (414 ml)</t>
+          <t>Rapid Ceramic Paint Sealant (12 oz.)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4337,42 +4045,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA1</t>
+          <t>AH-RCINT14A1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B0B94G13CN</t>
+          <t>B0DKVZRX69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Paint Sealant (12 oz.)</t>
+          <t>Rapid Ceramic Interior Detailer (414 ml)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4399,7 +4107,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4412,7 +4120,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4420,17 +4128,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>42.3</v>
+        <v>39</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -4457,7 +4165,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4470,7 +4178,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -4478,17 +4186,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>109.1</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4629,7 +4337,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1361</v>
+        <v>1205</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4642,7 +4350,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1361</v>
+        <v>1205</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -4650,17 +4358,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>24.8</v>
+        <v>20.7</v>
       </c>
       <c r="J2" t="n">
-        <v>925</v>
+        <v>804</v>
       </c>
       <c r="K2" t="n">
-        <v>1470</v>
+        <v>1890</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -4683,42 +4391,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-TRKITA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B0FYRJ1966</t>
+          <t>B07SHJVK4G</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rapid Ceramic Plastic Restorer and Protectant</t>
+          <t>Ceramic Trim Coat Kit</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.9</v>
+        <v>75.2</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -4745,7 +4453,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4758,7 +4466,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>386</v>
+        <v>342</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4766,17 +4474,17 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -4799,24 +4507,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA</t>
+          <t>AH-RCPL-B14A</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>362</v>
+        <v>196</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B0B94G13CN</t>
+          <t>B0FYRJ1966</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platinum Rapid Ceramic Paint Sealant Spray</t>
+          <t>Rapid Ceramic Plastic Restorer and Protectant</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>362</v>
+        <v>196</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4824,17 +4532,17 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>18.1</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4857,42 +4565,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AH-TRKITA</t>
+          <t>AH-RCPAINTA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>355</v>
+        <v>149</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B07SHJVK4G</t>
+          <t>B0B94G13CN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ceramic Trim Coat Kit</t>
+          <t>Platinum Rapid Ceramic Paint Sealant Spray</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>355</v>
+        <v>149</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="J6" t="n">
-        <v>440</v>
+        <v>83</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4919,7 +4627,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4932,7 +4640,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4940,17 +4648,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="J7" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -4977,7 +4685,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4990,7 +4698,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5008,7 +4716,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5035,7 +4743,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5048,25 +4756,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>BELOW_TARGET</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>78.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5093,7 +4801,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5106,7 +4814,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5114,7 +4822,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>57.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>16</v>
@@ -5124,7 +4832,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5155,7 +4863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5265,7 +4973,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5278,7 +4986,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -5286,17 +4994,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>21.8</v>
+        <v>20.5</v>
       </c>
       <c r="J2" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K2" t="n">
         <v>68</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -5319,42 +5027,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C-148TA</t>
+          <t>C-246TA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B0CJRXFW47</t>
+          <t>B0CJRVC2N9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C-Series Burnt Bronze Ceramic Coating</t>
+          <t>C-Series Flat Dark Earth Ceramic Coating</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5377,24 +5085,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C-102TA</t>
+          <t>C-7600PA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B0CJRTVXWG</t>
+          <t>B0CJRVJFPR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C-Series Graphite Black Ceramic Coating</t>
+          <t>C-Series Glacier Black High-Temp Coating</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5402,17 +5110,17 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>8.1</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5435,42 +5143,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C-246TA</t>
+          <t>C-148TA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B0CJRVC2N9</t>
+          <t>B0CJRXFW47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C-Series Flat Dark Earth Ceramic Coating</t>
+          <t>C-Series Burnt Bronze Ceramic Coating</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -5493,24 +5201,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H-148TA</t>
+          <t>C-102TA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B0CL17YW21</t>
+          <t>B0CJRTVXWG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t>C-Series Graphite Black Ceramic Coating</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -5518,17 +5226,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>22.5</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5551,24 +5259,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C-7600PA</t>
+          <t>H-148TA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B0CJRVJFPR</t>
+          <t>B0CL17YW21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C-Series Glacier Black High-Temp Coating</t>
+          <t>H-Series Ceramic Coating</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -5576,17 +5284,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>11.7</v>
+        <v>42.3</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="K7" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5613,7 +5321,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5626,7 +5334,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -5634,17 +5342,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>52.2</v>
+        <v>47.4</v>
       </c>
       <c r="J8" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5667,42 +5375,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H-146P</t>
+          <t>C-192TA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B0CL14BYN9</t>
+          <t>B0CJRWGTJN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>(Oven Cure) H-Series Graphite Black [ 16oz ] H-146P</t>
+          <t>(AIR Cure C-Series Armor Black [ 4oz ] C-192T Performance Ce</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5725,24 +5433,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C-192TA</t>
+          <t>C-244TA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B0CJRWGTJN</t>
+          <t>B0CJRW4X3S</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(AIR Cure C-Series Armor Black [ 4oz ] C-192T Performance Ce</t>
+          <t>C-Series MIL-SPEC O.D. Green Ceramic Coating</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -5750,17 +5458,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5783,24 +5491,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C-297T</t>
+          <t>H-146P</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B0D6GTWV2Q</t>
+          <t>B0CL14BYN9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>(AIR Cure C-Series Aqua Teal (4 oz) C-297T</t>
+          <t>(Oven Cure) H-Series Graphite Black [ 16oz ] H-146P</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5818,7 +5526,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5841,24 +5549,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C-298T</t>
+          <t>C-163T</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B0D62HLLLB</t>
+          <t>B0CJRWHHFY</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>(AIR Cure C-Series Black Cherry (4 oz) C-298T</t>
+          <t>C-Series Lollypop Purple Ceramic Coating</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5876,7 +5584,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5899,42 +5607,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SE-146</t>
+          <t>H-109TA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B0BZTX44PW</t>
+          <t>B0CL15VMJS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Iwata LPH80 Needle Packing KIT</t>
+          <t>H-Series Ceramic Coating</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>51.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5957,7 +5665,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C-7300T</t>
+          <t>C-297T</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5965,12 +5673,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B0CJRVN17X</t>
+          <t>B0D6GTWV2Q</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">(AIR Cure C-Series Black Velvet [ 4oz ] C-7300T Performance </t>
+          <t>(AIR Cure C-Series Aqua Teal (4 oz) C-297T</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -5992,7 +5700,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6015,24 +5723,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C-163T</t>
+          <t>C-298T</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B0CJRWHHFY</t>
+          <t>B0D62HLLLB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C-Series Lollypop Purple Ceramic Coating</t>
+          <t>(AIR Cure C-Series Black Cherry (4 oz) C-298T</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -6050,7 +5758,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6073,24 +5781,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H-261P</t>
+          <t>SE-146</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B0CL1824QF</t>
+          <t>B0BZTX44PW</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t>Iwata LPH80 Needle Packing KIT</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -6108,7 +5816,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6131,24 +5839,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H-217T</t>
+          <t>C-7300T</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B0CL1967DY</t>
+          <t>B0CJRVN17X</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t xml:space="preserve">(AIR Cure C-Series Black Velvet [ 4oz ] C-7300T Performance </t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -6166,7 +5874,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -6189,42 +5897,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H-TOP3KITA</t>
+          <t>H-261P</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B081J7XGV3</t>
+          <t>B0CL1824QF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>H-SeriesTop Colors Starter Kit (H-146</t>
+          <t>H-Series Ceramic Coating</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -6247,42 +5955,42 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C-244TA</t>
+          <t>H-217T</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B0CJRW4X3S</t>
+          <t>B0CL1967DY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C-Series MIL-SPEC O.D. Green Ceramic Coating</t>
+          <t>H-Series Ceramic Coating</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BELOW_FLOOR</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -6305,24 +6013,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H-190Q</t>
+          <t>C-102Q</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>B0CL17TZXW</t>
+          <t>B0CJRW4LR7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t>C-Series Graphite Black Ceramic Coating</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -6340,7 +6048,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -6363,7 +6071,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C-102Q</t>
+          <t>H-190Q</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6371,12 +6079,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>B0CJRW4LR7</t>
+          <t>B0CL17TZXW</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C-Series Graphite Black Ceramic Coating</t>
+          <t>H-Series Ceramic Coating</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6398,7 +6106,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -6421,15 +6129,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H-109TA</t>
+          <t>H-144P</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>B0CL15VMJS</t>
+          <t>B0CL14MZNJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6438,25 +6146,25 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BELOW_TARGET</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>64.2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -6479,7 +6187,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H-144P</t>
+          <t>H-305T</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6487,7 +6195,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>B0CL14MZNJ</t>
+          <t>B0CL1DBH4X</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6514,7 +6222,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -6537,7 +6245,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H-305T</t>
+          <t>H-112T</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6545,7 +6253,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>B0CL1DBH4X</t>
+          <t>B0CL1BCTJV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6572,7 +6280,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -6595,7 +6303,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H-112T</t>
+          <t>C-211P</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6603,12 +6311,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>B0CL1BCTJV</t>
+          <t>B0CJRVHFS3</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t>(AIR Cure C-Series Desert Sand (16oz) |C-211P|-Our Ceramic T</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6630,7 +6338,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -6653,7 +6361,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C-211P</t>
+          <t>H-264P</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6661,12 +6369,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>B0CJRVHFS3</t>
+          <t>B0CL14JSLD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(AIR Cure C-Series Desert Sand (16oz) |C-211P|-Our Ceramic T</t>
+          <t>H-Series Ceramic Coating</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6688,7 +6396,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -6711,7 +6419,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H-212T</t>
+          <t>H-200T</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6719,7 +6427,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>B0CL15LDG8</t>
+          <t>B0CL12B4KN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6746,7 +6454,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -6769,7 +6477,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H-264P</t>
+          <t>H-256T</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6777,7 +6485,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>B0CL14JSLD</t>
+          <t>B0CL15PHR3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6804,7 +6512,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -6827,7 +6535,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H-200T</t>
+          <t>H-247T</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6835,7 +6543,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>B0CL12B4KN</t>
+          <t>B0CL16479S</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6862,7 +6570,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -6885,7 +6593,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>H-256T</t>
+          <t>FX-106A</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6893,12 +6601,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>B0CL15PHR3</t>
+          <t>B0DHX2FD97</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t>FX™ Ranger (4g) FX-106A</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6920,7 +6628,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -6943,7 +6651,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>H-310T</t>
+          <t>C-242P</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6951,12 +6659,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B0CL16FHZL</t>
+          <t>B0CJRV8C2S</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>H-Series Ceramic Coating</t>
+          <t>C-Series Hidden White Ceramic Coating</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6978,7 +6686,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -6993,122 +6701,6 @@
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>H-247T</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>B0CL16479S</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>H-Series Ceramic Coating</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>MISSING: NIC to add units per box</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FX-106A</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>B0DHX2FD97</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>FX™ Ranger (4g) FX-106A</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>MISSING: NIC to add units per box</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
         <is>
           <t>US</t>
         </is>
@@ -7125,7 +6717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7231,24 +6823,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>USS-2603A</t>
+          <t>PSS-11248A</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B08C5KXZQK</t>
+          <t>B0CWVWKS22</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS Gloss Black Urethane Powder Coating</t>
+          <t>PRISMATIC POWDERS High Gloss Black Polyester Powder Coating</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -7256,17 +6848,17 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.4</v>
+        <v>11.3</v>
       </c>
       <c r="J2" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -7289,24 +6881,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PPS-2974A</t>
+          <t>USS-2603A</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B00MI5357U</t>
+          <t>B08C5KXZQK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS Clear Vision Polyester Clear Powder Coatin</t>
+          <t>PRISMATIC POWDERS Gloss Black Urethane Powder Coating</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -7314,17 +6906,17 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9.9</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="K3" t="n">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -7347,24 +6939,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSS-11248A</t>
+          <t>PPS-2974A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B0CWVWKS22</t>
+          <t>B00MI5357U</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS High Gloss Black Polyester Powder Coating</t>
+          <t>PRISMATIC POWDERS Clear Vision Polyester Clear Powder Coatin</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -7372,17 +6964,17 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>15.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -7409,7 +7001,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7422,7 +7014,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -7430,17 +7022,17 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="J5" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="K5" t="n">
         <v>68</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -7467,7 +7059,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -7480,7 +7072,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7498,7 +7090,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -7525,7 +7117,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7538,7 +7130,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -7546,17 +7138,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
         <v>68</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -7579,24 +7171,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PPS-4442A</t>
+          <t>PSS-5690A</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B0CXW3SMH8</t>
+          <t>B00MI516TO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS Candy Purple Transparent Powder Coating</t>
+          <t>PRISMATIC POWDERS Gloss White Polyester Powder Coating</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7604,17 +7196,17 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>16.3</v>
+        <v>24.1</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -7624,10 +7216,14 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>only FBA SKU</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>top FBA SKU by 30-day FBA units</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PSS-5690</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>US</t>
@@ -7637,24 +7233,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSS-5690A</t>
+          <t>PPS-4442A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B00MI516TO</t>
+          <t>B0CXW3SMH8</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS Gloss White Polyester Powder Coating</t>
+          <t>PRISMATIC POWDERS Candy Purple Transparent Powder Coating</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -7662,17 +7258,17 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>31.1</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -7682,14 +7278,10 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>top FBA SKU by 30-day FBA units</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>PSS-5690</t>
-        </is>
-      </c>
+          <t>only FBA SKU</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>US</t>
@@ -7703,7 +7295,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -7716,7 +7308,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -7724,17 +7316,17 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>27.7</v>
+        <v>20.9</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
         <v>34</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -7761,7 +7353,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -7774,7 +7366,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -7782,17 +7374,17 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>49.6</v>
+        <v>48.5</v>
       </c>
       <c r="J11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -7815,7 +7407,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>USS-1522A</t>
+          <t>PSS-11181A</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -7823,12 +7415,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B00MI56YHI</t>
+          <t>B0CWWJJYS1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS® Black Jack (1 LB/USS-1522)</t>
+          <t>PRISMATIC POWDERS Super Durable Matte Black Powder Coating</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -7840,17 +7432,17 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>31.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -7908,7 +7500,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -7931,42 +7523,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ESS-11151A</t>
+          <t>USS-1522A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B0BW26CTFX</t>
+          <t>B00MI56YHI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS Zinc Primer</t>
+          <t>PRISMATIC POWDERS® Black Jack (1 LB/USS-1522)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>BELOW_FLOOR</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -7989,24 +7581,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PMB-6889</t>
+          <t>ESS-11151A</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>B0CWWL4KWK</t>
+          <t>B0BW26CTFX</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PRISMATIC POWDERS® Midnight Shadow (1 LB/PMB-6889)</t>
+          <t>PRISMATIC POWDERS Zinc Primer</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -8024,7 +7616,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -8051,38 +7643,38 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>B0CXW3XLKR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PRISMATIC POWDERS Lollypop Blue Transparent Powder Coating</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>BELOW_FLOOR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>B0CXW3XLKR</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>PRISMATIC POWDERS Lollypop Blue Transparent Powder Coating</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>BELOW_FLOOR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
       </c>
       <c r="K16" t="n">
         <v>34</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -8097,6 +7689,64 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PMB-6889</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>B0CWWL4KWK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PRISMATIC POWDERS® Midnight Shadow (1 LB/PMB-6889)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MISSING: NIC to add units per box</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>only FBA SKU</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>US</t>
         </is>
